--- a/南京三日游时间线总览.xlsx
+++ b/南京三日游时间线总览.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,12 +33,14 @@
     </font>
     <font>
       <name val="微软雅黑"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="微软雅黑"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -54,28 +56,10 @@
       <name val="微软雅黑"/>
       <b val="1"/>
       <color rgb="00C00000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -86,6 +70,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
         <bgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8D1F0"/>
+        <bgColor rgb="00E8D1F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
       </patternFill>
     </fill>
     <fill>
@@ -114,32 +110,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-        <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-        <bgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-        <bgColor rgb="00C00000"/>
       </patternFill>
     </fill>
   </fills>
@@ -161,78 +133,91 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -648,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -662,476 +647,2057 @@
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>南京三日游完整时间线总览 V3.4（纪念馆与博物院对调版）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="25" customHeight="1">
+          <t>南京三日游完整时间线总览 V3.8（住宿确定·中山南路369号）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>适用人群：3位17岁学生  |  总预算：人均1700元  |  2026年7月14日-17日</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
+          <t>日期/时段</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>行程安排</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>交通/步行</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>费用(元)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>注意事项</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>7月14日（周二）</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>7月15日（周三）</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>7月16日（周四）</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>7月17日（周五）</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>费用(人均)</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>到达南宁吴圩T2</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>起床洗漱</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>早餐豆浆油条</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>早餐</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>起飞 MU2966</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>早餐+出发：民宿附近</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>地铁→苜蓿园</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>地铁→云锦路</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="n"/>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>★ 地铁→明故宫</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>明孝陵游览 ¥35（学生票）</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>★ 纪念馆 08:30-10:30（免费）</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="14" t="inlineStr">
-        <is>
-          <t>★高考生免预约</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>抵达禄口机场 01:50</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>★ 南京博物院 09:00-11:30（免费）</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>梧桐大道拍照</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>地铁→大行宫</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>提前7天预约</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>打车去市区</t>
+          <t>🏠 住宿确认：中山南路369号「巨幕MaX投影No.8赋闲洛畔」⭐4.9 | 三山街站步行3min</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>🏠 民宿</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>7/14-7/17</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>中山南路369号·巨幕投影·电梯·ins风</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>三山街站3号口步行246m/3min</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>¥50-60/晚</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>提前联系房东确认密码</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>📍 坐标</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>118.782038,32.022953（高德精确校验）</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>近秦淮河/夫子庙/老门东</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>📅 7月14日（周二）—— 出发 + 浦口半日游（轮渡+民国风情）</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>🛫 出发</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>地铁→大行宫</t>
+          <t>中午</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>中山陵游览（免费）</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>科巷午餐 ¥25</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="12" t="n"/>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>入住民宿 03:00</t>
+          <t>出发去南宁吴圩机场，登机飞往南京</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>地铁/打车去机场</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>机票¥600</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>提前24h线上值机！充电宝随身带</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>🛬 抵达</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>科巷午餐 ¥30</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>音乐台喂鸽子 ¥5（学生票）</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>地铁→三山街</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>睡觉至次日08:00</t>
+          <t>抵达南京禄口机场T2，取行李</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>约2.5h航班</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>取行李20-30min</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>🚇 去市区</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>总统府游览 ¥20（学生票）</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>午餐自带干粮 ¥15</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>取行李</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="8" t="n"/>
+          <t>地铁S1号线→南京南站→换1号线→三山街</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>约1h</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>¥8</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>下午有地铁，不用打车</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>🏠 入住</t>
+        </is>
+      </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>地铁→鸡鸣寺</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>紫金山天文台 ¥15（学生票）</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>地铁→南京站</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="8" t="n"/>
+          <t>★入住民宿（中山南路369号·巨幕投影）</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>三山街站3号口步行3min</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>民宿¥55</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>联系房东确认门禁/WiFi密码</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>🚇 浦口</t>
+        </is>
+      </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>鸡鸣寺烧香 ¥10（送三根香）</t>
+          <t>15:30-16:05</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>下山→地铁</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>到达南京站 12:10</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>★缓冲2h26min</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="8" t="n"/>
+          <t>地铁5号线：三山街→下关（中山码头）</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>纯地铁20min + 步行15min</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>¥3</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>直达！高德校验 ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>⛴️ 轮渡</t>
+        </is>
+      </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>步行→玄武湖</t>
+          <t>16:05-16:15</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>地铁回三山街</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>候车 12:10-14:10</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="8" t="n"/>
+          <t>中山码头→浦口码头（宁浦线轮渡）</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>约10分钟</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>¥2</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>★长江江景！远眺南京长江大桥</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>🚂 车站</t>
+        </is>
+      </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>玄武湖傍晚（免费）</t>
+          <t>16:30-17:15</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>回民宿休息</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>★ 火车出发！14:36</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>⚠️过路站确认站台</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="8" t="n"/>
+          <t>★浦口火车站旧址（《背影》同款）</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>浦口码头步行5min</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>免费</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>月台+铁轨拍照！百年老站</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>⛴️ 返程</t>
+        </is>
+      </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>地铁→三山街</t>
+          <t>17:15-17:25</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>晚餐民宿附近 ¥25</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="8" t="n"/>
+          <t>浦口码头→中山码头（轮渡返程）</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>约10分钟</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>¥2</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>轮渡约20-30分钟一班</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>🚂 火车园</t>
+        </is>
+      </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>老门东夜游（灯笼）</t>
+          <t>17:30-18:30</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>自由活动</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="8" t="n"/>
+          <t>★下关火车主题园（绿皮火车+长江日落）</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>中山码头步行15min</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>免费</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>★绿皮火车+长江日落！喷驱蚊液</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>🚇 返回</t>
+        </is>
+      </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>夫子庙简游+晚餐 ¥35</t>
+          <t>18:30-19:10</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>回民宿</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="8" t="n"/>
+          <t>盐仓桥→三山街（地铁5号线）→步行3min回民宿</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>纯地铁20min + 步行12min</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>¥3</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>高德校验 ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>🍜 晚餐</t>
+        </is>
+      </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>秦淮河夜游（免费）</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="8" t="n"/>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>回民宿休息</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="11" t="n"/>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>民宿附近晚餐（鸭血粉丝汤+锅贴）</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>步行</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>¥25</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>买好明天早餐干粮</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>今日费用</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>机票¥600 + 地铁¥14 + 轮渡¥4 + 餐饮¥25 + 民宿¥55 = 约¥698</t>
+        </is>
+      </c>
       <c r="E19" s="12" t="n"/>
       <c r="F19" s="12" t="n"/>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>每日费用汇总</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>7月14日
-机票600 + 打车45 = 645元</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>7月15日
-交通7 + 门票30 + 餐饮75 + 住宿55 = 167元</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>7月16日
-地铁6 + 门票55 + 餐饮48 = 109元</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>7月17日
-地铁10 + 餐饮55 = 65元</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
-        <is>
-          <t>三日合计：约986元
-（不含大交通953元）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>交通票务</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="25" customHeight="1">
-      <c r="A24" s="22" t="inlineStr">
-        <is>
-          <t>MU2966  南宁吴圩T2  23:25 → 南京禄口T2  01:50(+1)</t>
-        </is>
-      </c>
-      <c r="D24" s="23" t="inlineStr">
-        <is>
-          <t>经济舱  ¥600</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="25" customHeight="1">
-      <c r="A25" s="22" t="inlineStr">
-        <is>
-          <t>K1557   南京站  14:36 → 南宁站  15:35(+1)</t>
-        </is>
-      </c>
-      <c r="D25" s="23" t="inlineStr">
-        <is>
-          <t>硬卧  ¥353</t>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>📅 7月15日（周三）—— 金陵文博线（博物院+总统府+鸡鸣寺+玄武湖+老门东+秦淮河）</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>🌅 起床</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>起床洗漱，民宿附近早餐</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>步行</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>¥10</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>豆浆+包子/锅贴</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>🚇 出发</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>地铁1号线→2号线：三山街→明故宫</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>纯地铁15min + 步行3min</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>¥3</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>高德校验 ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>🏛️ 博物院</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>09:00-11:30</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>南京博物院（历史馆→特展馆→民国馆）</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>明故宫站5号口步行5min</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>免费</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>⚠️9:00开门！提前7天预约</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>🚇 科巷</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>11:30-11:45</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>地铁2号线：明故宫→大行宫</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>纯地铁7min + 步行4min</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>¥2</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>高德校验 ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>🍜 午餐</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>11:45-12:30</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>科巷美食街（鸭血粉丝汤+汤包+藕饼）</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>大行宫站步行3min</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>¥30</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>鸿福面馆/鸡鸣汤包</t>
         </is>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
-        <is>
-          <t>总预算</t>
-        </is>
-      </c>
-      <c r="D27" s="24" t="inlineStr">
-        <is>
-          <t>约 ¥1518-1538 / 人（预留162元弹性，总控1700）</t>
-        </is>
-      </c>
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>🏛️ 总统府</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>12:30-15:00</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>总统府（中轴线→东花园→西花园→1912）</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>大行宫站5号口步行5min</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>学生¥20</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>⚠️提前5天预约！带学生证</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>🚇 鸡鸣寺</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>15:00-15:10</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>地铁3号线：大行宫→鸡鸣寺</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>纯地铁8min + 步行2min</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>¥2</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>高德校验 ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>🏯 鸡鸣寺</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>15:30-16:30</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>鸡鸣寺（南门进→天王殿→药师佛塔→北门出）</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>鸡鸣寺站5号口步行5min</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>¥10</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>送三根香！单行道南进北出</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>🏞️ 玄武湖</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>16:30-18:00</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>玄武湖傍晚游（解放门→环洲→梁洲→玄武门）</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>鸡鸣寺北门步行5min</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>免费</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>★夕阳湖面金光！荷花池</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>🚇 返回</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>18:00-18:20</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>地铁1号线：玄武门→三山街→步行3min回民宿</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>纯地铁13min + 步行7min</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>¥3</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>高德校验 ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>🏮 老门东</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>18:30-19:15</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>老门东夜游（牌坊→三条营→先锋书店→红灯笼）</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>民宿步行8min</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>免费</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>★灯笼夜景！如千与千寻</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>🍜 晚餐</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>19:15-19:30</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>老门东/夫子庙小吃（南京烤鸭+鸭血粉丝）</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>步行</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>¥35</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>韩复兴/桂花鸭</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>🏮 夫子庙</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>19:30-20:00</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>夫子庙精简游（大成殿外→文德桥）</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>步行</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>免费</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>不进殿（省¥35）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>🏮 秦淮河</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>20:00-21:30</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>夜游秦淮河（文德桥→桃叶渡→白鹭洲公园）</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>步行</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>免费</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>游船¥80不建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>🏠 回民宿</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>步行回民宿休息（中山南路369号）</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>步行8min</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>提前买好明天干粮</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>今日费用</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="18" t="inlineStr">
+        <is>
+          <t>交通¥7 + 门票¥30 + 餐饮¥75 + 住宿¥55 = ¥167</t>
+        </is>
+      </c>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="17" t="n"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>📅 7月16日（周四）—— 钟山全天深度游（明孝陵免费+紫金山登山+灵谷寺）</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>🌅 起床</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>★超早起！洗漱，民宿内吃早餐（提前买好干粮）</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>¥8</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>★6:30前到明孝陵免费！</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>🚇 出发</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>05:45-06:15</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>地铁1号线→2号线：三山街→苜蓿园</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>纯地铁17min + 步行3min</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>¥3</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>高德校验 ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>🏛️ 明孝陵</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>06:20-08:20</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>★明孝陵（6:30前免费入场！3号门进）</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>苜蓿园站1号口步行10min</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>★免费！</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>★省¥70！石象路晨光绝美</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>🌳 梧桐大道</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>08:20-09:15</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>梧桐大道·陵园路（丁达尔光线拍照）</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>明孝陵步行15min</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>免费</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>★树冠遮天！路中间安全岛拍</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>🏛️ 中山陵</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>09:15-11:15</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>中山陵（博爱坊→392级台阶→祭堂）</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>沿梧桐大道步行20min</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>免费</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>⚠️预约8:30-10:30！带身份证</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>🕊️ 音乐台</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>11:15-12:15</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>音乐台（喂鸽子！自带小面包省钱）</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>中山陵旁步行5min</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>学生¥5</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>★鸽子起飞拍照！带学生证</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>🍞 午餐</t>
+        </is>
+      </c>
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>12:15-12:45</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>自带干粮（面包+火腿肠+水）</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>音乐台台阶/树荫</t>
+        </is>
+      </c>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>¥15</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>景区餐饮贵，自带省钱</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>🏔️ 紫金山</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>12:30-14:30</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>★爬紫金山！音乐台→头陀岭（448.9m）→山顶停留</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>登山约1.5h + 山顶30min</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>★免费！</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>★俯瞰南京全景！带足水2瓶/人</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>🚶 下山</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>14:30-15:30</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>头陀岭→灵谷寺（水榭路→环紫金山绿道）</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>下山约1h</t>
+        </is>
+      </c>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>注意膝盖！侧身走省力</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>🏯 灵谷寺</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>15:30-16:45</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>★灵谷寺（无梁殿→灵谷塔→松风阁）</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>灵谷景区南门进</t>
+        </is>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>学生¥18</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>★灵谷塔9层俯瞰钟山！喷驱蚊液</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>🚌 返回</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>16:45-17:30</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>202路公交→孝陵卫→地铁2号线→1号线→三山街→步行3min回民宿</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>公交14min+地铁21min+步行</t>
+        </is>
+      </c>
+      <c r="E50" s="20" t="inlineStr">
+        <is>
+          <t>¥5</t>
+        </is>
+      </c>
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>高德校验 ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>🏠 休息</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>17:30-19:00</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>回民宿休息（中山南路369号，洗澡+躺平）</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>步行3min</t>
+        </is>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>4万步+含登山，必须休息！</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>🍜 晚餐</t>
+        </is>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t>民宿附近晚餐（鸭血粉丝汤+锅贴+梅花糕）</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>步行</t>
+        </is>
+      </c>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
+          <t>¥25</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>本地人吃的小店</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>🌙 休息</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>回民宿休息</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>明天是最后一天，养精蓄锐</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="21" t="inlineStr">
+        <is>
+          <t>今日费用</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="n"/>
+      <c r="C54" s="22" t="n"/>
+      <c r="D54" s="23" t="inlineStr">
+        <is>
+          <t>交通¥8 + 门票¥23（音乐台5+灵谷寺18） + 餐饮¥48 = ¥79</t>
+        </is>
+      </c>
+      <c r="E54" s="22" t="n"/>
+      <c r="F54" s="22" t="n"/>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>📅 7月17日（周五）—— ⚠️ 半日铭记线 + 返程（火车14:36发车！）</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n"/>
+      <c r="C56" s="8" t="n"/>
+      <c r="D56" s="8" t="n"/>
+      <c r="E56" s="8" t="n"/>
+      <c r="F56" s="8" t="n"/>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="24" t="inlineStr">
+        <is>
+          <t>🌅 起床</t>
+        </is>
+      </c>
+      <c r="B57" s="24" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C57" s="25" t="inlineStr">
+        <is>
+          <t>起床洗漱，打包所有行李，退房</t>
+        </is>
+      </c>
+      <c r="D57" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E57" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="25" t="inlineStr">
+        <is>
+          <t>行李寄存民宿前台</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="24" t="inlineStr">
+        <is>
+          <t>🍜 早餐</t>
+        </is>
+      </c>
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="C58" s="25" t="inlineStr">
+        <is>
+          <t>民宿附近早餐（小馄饨+烧饼）</t>
+        </is>
+      </c>
+      <c r="D58" s="25" t="inlineStr">
+        <is>
+          <t>步行5min</t>
+        </is>
+      </c>
+      <c r="E58" s="25" t="inlineStr">
+        <is>
+          <t>¥10</t>
+        </is>
+      </c>
+      <c r="F58" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="32" customHeight="1">
+      <c r="A59" s="24" t="inlineStr">
+        <is>
+          <t>🚇 出发</t>
+        </is>
+      </c>
+      <c r="B59" s="24" t="inlineStr">
+        <is>
+          <t>08:00-08:25</t>
+        </is>
+      </c>
+      <c r="C59" s="25" t="inlineStr">
+        <is>
+          <t>地铁1号线→2号线：三山街→云锦路</t>
+        </is>
+      </c>
+      <c r="D59" s="25" t="inlineStr">
+        <is>
+          <t>纯地铁16min + 步行4min</t>
+        </is>
+      </c>
+      <c r="E59" s="25" t="inlineStr">
+        <is>
+          <t>¥3</t>
+        </is>
+      </c>
+      <c r="F59" s="25" t="inlineStr">
+        <is>
+          <t>高德校验 ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>🕯️ 纪念馆</t>
+        </is>
+      </c>
+      <c r="B60" s="24" t="inlineStr">
+        <is>
+          <t>08:30-10:30</t>
+        </is>
+      </c>
+      <c r="C60" s="25" t="inlineStr">
+        <is>
+          <t>★侵华日军南京大屠杀遇难同胞纪念馆</t>
+        </is>
+      </c>
+      <c r="D60" s="25" t="inlineStr">
+        <is>
+          <t>云锦路站2号口步行2min</t>
+        </is>
+      </c>
+      <c r="E60" s="25" t="inlineStr">
+        <is>
+          <t>免费</t>
+        </is>
+      </c>
+      <c r="F60" s="25" t="inlineStr">
+        <is>
+          <t>🎓高考生免预约！带准考证+身份证</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="24" t="inlineStr">
+        <is>
+          <t>🚇 科巷</t>
+        </is>
+      </c>
+      <c r="B61" s="24" t="inlineStr">
+        <is>
+          <t>10:30-10:50</t>
+        </is>
+      </c>
+      <c r="C61" s="25" t="inlineStr">
+        <is>
+          <t>地铁2号线：云锦路→大行宫</t>
+        </is>
+      </c>
+      <c r="D61" s="25" t="inlineStr">
+        <is>
+          <t>纯地铁14min + 步行4min</t>
+        </is>
+      </c>
+      <c r="E61" s="25" t="inlineStr">
+        <is>
+          <t>¥2</t>
+        </is>
+      </c>
+      <c r="F61" s="25" t="inlineStr">
+        <is>
+          <t>高德校验 ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="24" t="inlineStr">
+        <is>
+          <t>🍜 午餐</t>
+        </is>
+      </c>
+      <c r="B62" s="24" t="inlineStr">
+        <is>
+          <t>10:50-11:20</t>
+        </is>
+      </c>
+      <c r="C62" s="25" t="inlineStr">
+        <is>
+          <t>科巷午餐（鸭血粉丝汤+藕饼+烧饼）</t>
+        </is>
+      </c>
+      <c r="D62" s="25" t="inlineStr">
+        <is>
+          <t>大行宫站步行3min</t>
+        </is>
+      </c>
+      <c r="E62" s="25" t="inlineStr">
+        <is>
+          <t>¥25</t>
+        </is>
+      </c>
+      <c r="F62" s="25" t="inlineStr">
+        <is>
+          <t>快速吃，不要逗留！</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" s="24" t="inlineStr">
+        <is>
+          <t>🚇 取行李</t>
+        </is>
+      </c>
+      <c r="B63" s="24" t="inlineStr">
+        <is>
+          <t>11:20-11:40</t>
+        </is>
+      </c>
+      <c r="C63" s="25" t="inlineStr">
+        <is>
+          <t>地铁2号线→1号线：大行宫→三山街→步行3min取行李</t>
+        </is>
+      </c>
+      <c r="D63" s="25" t="inlineStr">
+        <is>
+          <t>纯地铁11min + 换乘+步行</t>
+        </is>
+      </c>
+      <c r="E63" s="25" t="inlineStr">
+        <is>
+          <t>¥2</t>
+        </is>
+      </c>
+      <c r="F63" s="25" t="inlineStr">
+        <is>
+          <t>快速取行李！不要磨蹭</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="24" t="inlineStr">
+        <is>
+          <t>🚇 南京站</t>
+        </is>
+      </c>
+      <c r="B64" s="24" t="inlineStr">
+        <is>
+          <t>11:50-12:10</t>
+        </is>
+      </c>
+      <c r="C64" s="25" t="inlineStr">
+        <is>
+          <t>地铁1号线：三山街→南京站（11号口）</t>
+        </is>
+      </c>
+      <c r="D64" s="25" t="inlineStr">
+        <is>
+          <t>纯地铁17min + 步行2min</t>
+        </is>
+      </c>
+      <c r="E64" s="25" t="inlineStr">
+        <is>
+          <t>¥3</t>
+        </is>
+      </c>
+      <c r="F64" s="25" t="inlineStr">
+        <is>
+          <t>⚠️最晚11:50必须出发！</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="24" t="inlineStr">
+        <is>
+          <t>🚂 候车</t>
+        </is>
+      </c>
+      <c r="B65" s="24" t="inlineStr">
+        <is>
+          <t>12:10-14:10</t>
+        </is>
+      </c>
+      <c r="C65" s="25" t="inlineStr">
+        <is>
+          <t>南京站候车（买零食+水），确认K1557车次</t>
+        </is>
+      </c>
+      <c r="D65" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="25" t="inlineStr">
+        <is>
+          <t>¥20</t>
+        </is>
+      </c>
+      <c r="F65" s="25" t="inlineStr">
+        <is>
+          <t>⚠️K1557是过路站！确认站台</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>🚂 返程</t>
+        </is>
+      </c>
+      <c r="B66" s="24" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="C66" s="25" t="inlineStr">
+        <is>
+          <t>★K1557次火车出发！南京→南宁</t>
+        </is>
+      </c>
+      <c r="D66" s="25" t="inlineStr">
+        <is>
+          <t>24h59min硬卧</t>
+        </is>
+      </c>
+      <c r="E66" s="25" t="inlineStr">
+        <is>
+          <t>¥353</t>
+        </is>
+      </c>
+      <c r="F66" s="25" t="inlineStr">
+        <is>
+          <t>7月18日15:35到达南宁</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="26" t="inlineStr">
+        <is>
+          <t>今日费用</t>
+        </is>
+      </c>
+      <c r="B67" s="27" t="n"/>
+      <c r="C67" s="27" t="n"/>
+      <c r="D67" s="28" t="inlineStr">
+        <is>
+          <t>交通¥10 + 门票¥0 + 餐饮¥55 = ¥65</t>
+        </is>
+      </c>
+      <c r="E67" s="27" t="n"/>
+      <c r="F67" s="27" t="n"/>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>💰 预算汇总（人均）</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n"/>
+      <c r="C69" s="8" t="n"/>
+      <c r="D69" s="8" t="n"/>
+      <c r="E69" s="8" t="n"/>
+      <c r="F69" s="8" t="n"/>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="29" t="inlineStr">
+        <is>
+          <t>机票</t>
+        </is>
+      </c>
+      <c r="B70" s="30" t="inlineStr">
+        <is>
+          <t>¥600</t>
+        </is>
+      </c>
+      <c r="C70" s="31" t="n"/>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>南宁→南京</t>
+        </is>
+      </c>
+      <c r="E70" s="31" t="n"/>
+      <c r="F70" s="31" t="n"/>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="29" t="inlineStr">
+        <is>
+          <t>硬卧K1557</t>
+        </is>
+      </c>
+      <c r="B71" s="30" t="inlineStr">
+        <is>
+          <t>¥353</t>
+        </is>
+      </c>
+      <c r="C71" s="31" t="n"/>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>南京→南宁</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="n"/>
+      <c r="F71" s="31" t="n"/>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="29" t="inlineStr">
+        <is>
+          <t>民宿3晚</t>
+        </is>
+      </c>
+      <c r="B72" s="30" t="inlineStr">
+        <is>
+          <t>¥150-180</t>
+        </is>
+      </c>
+      <c r="C72" s="31" t="n"/>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>中山南路369号·巨幕投影</t>
+        </is>
+      </c>
+      <c r="E72" s="31" t="n"/>
+      <c r="F72" s="31" t="n"/>
+    </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="29" t="inlineStr">
+        <is>
+          <t>门票总计</t>
+        </is>
+      </c>
+      <c r="B73" s="30" t="inlineStr">
+        <is>
+          <t>¥53</t>
+        </is>
+      </c>
+      <c r="C73" s="31" t="n"/>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>总统府¥20+鸡鸣寺¥10+音乐台¥5+灵谷寺¥18</t>
+        </is>
+      </c>
+      <c r="E73" s="31" t="n"/>
+      <c r="F73" s="31" t="n"/>
+    </row>
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="29" t="inlineStr">
+        <is>
+          <t>餐饮4天</t>
+        </is>
+      </c>
+      <c r="B74" s="30" t="inlineStr">
+        <is>
+          <t>¥245</t>
+        </is>
+      </c>
+      <c r="C74" s="31" t="n"/>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>含Day0晚餐+Day1-3三餐+火车零食</t>
+        </is>
+      </c>
+      <c r="E74" s="31" t="n"/>
+      <c r="F74" s="31" t="n"/>
+    </row>
+    <row r="75" ht="28" customHeight="1">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>市内交通</t>
+        </is>
+      </c>
+      <c r="B75" s="30" t="inlineStr">
+        <is>
+          <t>¥60</t>
+        </is>
+      </c>
+      <c r="C75" s="31" t="n"/>
+      <c r="D75" s="32" t="inlineStr">
+        <is>
+          <t>地铁+公交+轮渡</t>
+        </is>
+      </c>
+      <c r="E75" s="31" t="n"/>
+      <c r="F75" s="31" t="n"/>
+    </row>
+    <row r="76" ht="28" customHeight="1">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>机场地铁</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>¥8</t>
+        </is>
+      </c>
+      <c r="C76" s="31" t="n"/>
+      <c r="D76" s="32" t="inlineStr">
+        <is>
+          <t>禄口机场→市区</t>
+        </is>
+      </c>
+      <c r="E76" s="31" t="n"/>
+      <c r="F76" s="31" t="n"/>
+    </row>
+    <row r="77" ht="28" customHeight="1">
+      <c r="A77" s="29" t="inlineStr">
+        <is>
+          <t>备用金</t>
+        </is>
+      </c>
+      <c r="B77" s="30" t="inlineStr">
+        <is>
+          <t>¥80-100</t>
+        </is>
+      </c>
+      <c r="C77" s="31" t="n"/>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>零食/水/应急</t>
+        </is>
+      </c>
+      <c r="E77" s="31" t="n"/>
+      <c r="F77" s="31" t="n"/>
+    </row>
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>★合计</t>
+        </is>
+      </c>
+      <c r="B78" s="33" t="inlineStr">
+        <is>
+          <t>¥1519-1549</t>
+        </is>
+      </c>
+      <c r="C78" s="31" t="n"/>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>预留¥151-181弹性，总控¥1700</t>
+        </is>
+      </c>
+      <c r="E78" s="31" t="n"/>
+      <c r="F78" s="31" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D27:F27"/>
+  <mergeCells count="33">
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="D19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="B75:C75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
